--- a/stories/arbres/TREE-DIF-071.xlsx
+++ b/stories/arbres/TREE-DIF-071.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Maya est avec papa, dans le jardin. Maya a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya écoute papa. Maya entend les mots : énergie, pas une faute, jouer ou attendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Maya va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya respire. Maya retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Maya va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya respire. Maya retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Maya va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Maya se souvient : énergie, pas une faute, jouer ou attendre. Voici le geste : jouer ; attendre son tour ; demander à un adulte. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya respire. Maya retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. La lumière est claire. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le matin. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint après la sieste. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint le soir. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-071.xlsx
+++ b/stories/arbres/TREE-DIF-071.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Maya est avec papa, dans le jardin. Maya a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya écoute papa. Maya entend les mots : énergie, pas une faute, jouer ou attendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1873,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2045,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya respire. Maya retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2237,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2405,7 @@
           <t>narrateur|Maya a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2597,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2765,7 @@
           <t>narrateur|Maya rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2933,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3101,7 @@
           <t>narrateur|Maya rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3269,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3437,7 @@
           <t>narrateur|Maya rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3605,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3773,7 @@
           <t>narrateur|Maya a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3965,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4133,7 @@
           <t>narrateur|Maya rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4469,7 @@
           <t>narrateur|Maya rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4805,7 @@
           <t>narrateur|Maya rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4973,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5141,7 @@
           <t>narrateur|Maya a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5333,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5501,7 @@
           <t>narrateur|Maya rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5669,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5837,7 @@
           <t>narrateur|Maya rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6173,7 @@
           <t>narrateur|Maya rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya respire. Maya retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7058,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7226,7 @@
           <t>narrateur|Maya a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7418,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7586,7 @@
           <t>narrateur|Maya rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7754,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7922,7 @@
           <t>narrateur|Maya rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8090,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8258,7 @@
           <t>narrateur|Maya rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8426,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8594,7 @@
           <t>narrateur|Maya a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8786,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8954,7 @@
           <t>narrateur|Maya rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9290,7 @@
           <t>narrateur|Maya rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9626,7 @@
           <t>narrateur|Maya rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9794,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9962,7 @@
           <t>narrateur|Maya a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10154,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10322,7 @@
           <t>narrateur|Maya rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10658,7 @@
           <t>narrateur|Maya rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10994,7 @@
           <t>narrateur|Maya rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11331,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11515,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui bouge beaucoup.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11687,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya respire. Maya retient : énergie, pas une faute, jouer ou attendre. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11879,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12047,7 @@
           <t>narrateur|Maya a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12239,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12407,7 @@
           <t>narrateur|Maya rejoint le matin. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12575,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12743,7 @@
           <t>narrateur|Maya rejoint après la sieste. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12911,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13079,7 @@
           <t>narrateur|Maya rejoint le soir. La lumière est claire. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13415,7 @@
           <t>narrateur|Maya a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13607,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13775,7 @@
           <t>narrateur|Maya rejoint le matin. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14111,7 @@
           <t>narrateur|Maya rejoint après la sieste. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14447,7 @@
           <t>narrateur|Maya rejoint le soir. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14783,7 @@
           <t>narrateur|Maya a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya répète tout bas : énergie, pas une faute, jouer ou attendre. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14975,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15143,7 @@
           <t>narrateur|Maya rejoint le matin. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15479,7 @@
           <t>narrateur|Maya rejoint après la sieste. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15815,7 @@
           <t>narrateur|Maya rejoint le soir. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Maya a appris : Un camarade qui bouge beaucoup. Voici le geste : jouer ; attendre son tour ; demander à un adulte. Maya a entendu : énergie, pas une faute, jouer ou attendre. Maya dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16026,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16241,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-071.xlsx
+++ b/stories/arbres/TREE-DIF-071.xlsx
@@ -16467,7 +16467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16510,6 +16510,20 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/TREE-DIF-071.xlsx
+++ b/stories/arbres/TREE-DIF-071.xlsx
@@ -5329,17 +5329,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Le pli blanc tremble vers la porte. Près du battant, le vent pousse, fort. Mila lève le papier, trop tôt. J'ouvre, trop vite ! Le papier part de travers, pris. Le vent l'a pris ! Le battant claque, trop large. Ici, ça souffle trop. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?</t>
+          <t>Le pli blanc tremble vers la porte. Près du battant, le vent pousse, fort. Mila lève le papier, trop tôt. J'ouvre, trop vite ! Le papier part de travers, pris. Le vent l'a pris ! Le battant claque, trop large. Ici, ça souffle trop. Sans le vent, le papier irait droit. Alors on fait comment ? Tu vois comment, avec lui ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Le pli blanc tremble vers la porte. Près du battant, le &lt;emphasis level="moderate"&gt;vent&lt;/emphasis&gt; pousse, fort. Mila lève le papier, trop tôt. J'ouvre, trop vite ! Le papier part de travers, pris. Le vent l'a pris ! Le battant claque, trop large. Ici, ça souffle trop. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Le pli blanc tremble vers la porte. Près du battant, le &lt;emphasis level="moderate"&gt;vent&lt;/emphasis&gt; pousse, fort. Mila lève le papier, trop tôt. J'ouvre, trop vite ! Le papier part de travers, pris. Le vent l'a pris ! Le battant claque, trop large. Ici, ça souffle trop. Sans le vent, le papier irait droit. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Le pli blanc tremble vers la porte. Près du battant, le &lt;emphasis&gt;vent&lt;/emphasis&gt; pousse, fort. Mila lève le papier, trop tôt. J'ouvre, trop vite ! Le papier part de travers, pris. Le vent l'a pris ! Le battant claque, trop large. Ici, ça souffle trop. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Le pli blanc tremble vers la porte. Près du battant, le &lt;emphasis&gt;vent&lt;/emphasis&gt; pousse, fort. Mila lève le papier, trop tôt. J'ouvre, trop vite ! Le papier part de travers, pris. Le vent l'a pris ! Le battant claque, trop large. Ici, ça souffle trop. Sans le vent, le papier irait droit. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -5485,7 +5485,7 @@
 enfant-f|Le vent l'a pris !
 narrateur|Le battant claque, trop large.
 papa|Ici, ça souffle trop.
-maman|Il lui faut un air plus calme.
+maman|Sans le vent, le papier irait droit.
 enfant-f|Alors on fait comment ?
 papa|Tu vois comment, avec lui ?</t>
         </is>
@@ -8149,17 +8149,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Le nez lourd glisse entre les rayons, libre. Tu as tenu le guidon, loin du métal. La roue n'a plus attrapé le nez. Tes mains ont laissé le nez passer. On rentre, essuie le trombone. Le trombone reste froid, contre le nez. Le trombone reste froid, contre le nez plié.</t>
+          <t>Le nez lourd glisse entre les rayons, libre. Tu as tenu le guidon, loin du métal. La roue n'a plus attrapé le nez. Tes mains ont laissé le nez passer. On rentre, essuie le trombone. Le trombone brille un peu, contre le papier. Le trombone reste froid, contre le nez plié.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le nez lourd glisse entre les rayons, libre. Tu as tenu le &lt;emphasis level="moderate"&gt;guidon&lt;/emphasis&gt;, loin du métal. La roue n'a plus attrapé le nez. Tes mains ont laissé le nez passer. On rentre, essuie le trombone. Le trombone reste froid, contre le nez. Le trombone reste froid, contre le nez plié.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le nez lourd glisse entre les rayons, libre. Tu as tenu le &lt;emphasis level="moderate"&gt;guidon&lt;/emphasis&gt;, loin du métal. La roue n'a plus attrapé le nez. Tes mains ont laissé le nez passer. On rentre, essuie le trombone. Le trombone brille un peu, contre le papier. Le trombone reste froid, contre le nez plié.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le nez lourd glisse entre les rayons, libre. Tu as tenu le &lt;emphasis&gt;guidon&lt;/emphasis&gt;, loin du métal. La roue n'a plus attrapé le nez. Tes mains ont laissé le nez passer. On rentre, essuie le trombone. Le trombone reste froid, contre le nez. Le trombone reste froid, contre le nez plié.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le nez lourd glisse entre les rayons, libre. Tu as tenu le &lt;emphasis&gt;guidon&lt;/emphasis&gt;, loin du métal. La roue n'a plus attrapé le nez. Tes mains ont laissé le nez passer. On rentre, essuie le trombone. Le trombone brille un peu, contre le papier. Le trombone reste froid, contre le nez plié.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -8302,7 +8302,7 @@
 enfant-m|La roue n'a plus attrapé le nez.
 papa|Tes mains ont laissé le nez passer.
 maman|On rentre, essuie le trombone.
-narrateur|Le trombone reste froid, contre le nez.
+narrateur|Le trombone brille un peu, contre le papier.
 narrateur|Le trombone reste froid, contre le nez plié.</t>
         </is>
       </c>
@@ -10566,17 +10566,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Le nez trop lourd penche vers le seuil. Près de la porte, le vent pousse, large. Mila lève le trombone, trop tôt. Je tiens le battant, ouvert ! Le nez trop lourd plonge, trop vite. Il est tombé près du seuil ! Le papier file de côté, trop loin. Ici, le vent plus le poids, ça plonge. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?</t>
+          <t>Le nez trop lourd penche vers le seuil. Près de la porte, le vent pousse, large. Mila lève le trombone, trop tôt. Je tiens le battant, ouvert ! Le nez trop lourd plonge, trop vite. Il est tombé près du seuil ! Le papier file de côté, trop loin. Ici, le vent fait plonger le nez. Le nez a besoin d'un battant fermé. Alors on fait comment ? Tu vois comment, avec lui ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Le nez trop lourd penche vers le seuil. Près de la porte, le &lt;emphasis level="moderate"&gt;vent&lt;/emphasis&gt; pousse, large. Mila lève le trombone, trop tôt. Je tiens le battant, ouvert ! Le nez trop lourd plonge, trop vite. Il est tombé près du seuil ! Le papier file de côté, trop loin. Ici, le vent plus le poids, ça plonge. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Le nez trop lourd penche vers le seuil. Près de la porte, le &lt;emphasis level="moderate"&gt;vent&lt;/emphasis&gt; pousse, large. Mila lève le trombone, trop tôt. Je tiens le battant, ouvert ! Le nez trop lourd plonge, trop vite. Il est tombé près du seuil ! Le papier file de côté, trop loin. Ici, le vent fait plonger le nez. Le nez a besoin d'un battant fermé. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Le nez trop lourd penche vers le seuil. Près de la porte, le &lt;emphasis&gt;vent&lt;/emphasis&gt; pousse, large. Mila lève le trombone, trop tôt. Je tiens le battant, ouvert ! Le nez trop lourd plonge, trop vite. Il est tombé près du seuil ! Le papier file de côté, trop loin. Ici, le vent plus le poids, ça plonge. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Le nez trop lourd penche vers le seuil. Près de la porte, le &lt;emphasis&gt;vent&lt;/emphasis&gt; pousse, large. Mila lève le trombone, trop tôt. Je tiens le battant, ouvert ! Le nez trop lourd plonge, trop vite. Il est tombé près du seuil ! Le papier file de côté, trop loin. Ici, le vent fait plonger le nez. Le nez a besoin d'un battant fermé. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -10721,8 +10721,8 @@
 narrateur|Le nez trop lourd plonge, trop vite.
 enfant-f|Il est tombé près du seuil !
 narrateur|Le papier file de côté, trop loin.
-papa|Ici, le vent plus le poids, ça plonge.
-maman|Il lui faut un air plus calme.
+papa|Ici, le vent fait plonger le nez.
+maman|Le nez a besoin d'un battant fermé.
 enfant-f|Alors on fait comment ?
 papa|Tu vois comment, avec lui ?</t>
         </is>
@@ -13386,17 +13386,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Le long du blanc, l'avion glisse jusqu'à la porte. Tu as tenu, j'ai tracé. Le pneu n'a plus mangé la piste. Tes mains ont laissé la piste. On rentre, essuie tes doigts blancs. Un trait de craie sèche sur le ciment. Un trait de craie sèche sur le ciment, net.</t>
+          <t>Le long du blanc, l'avion glisse jusqu'à la porte. Tu as tenu, j'ai tracé. Le pneu n'a plus mangé la piste. Tes mains ont laissé la piste. On rentre, essuie tes doigts blancs. Un trait de craie sèche sous les guidons. Un trait de craie sèche sur le ciment, net.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le long du blanc, l'avion glisse jusqu'à la porte. Tu as tenu, j'ai tracé. Le pneu n'a plus mangé la piste. Tes mains ont laissé la piste. On rentre, essuie tes doigts blancs. Un trait de craie sèche sur le ciment. Un trait de craie sèche sur le ciment, net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le long du blanc, l'avion glisse jusqu'à la porte. Tu as tenu, j'ai tracé. Le pneu n'a plus mangé la piste. Tes mains ont laissé la piste. On rentre, essuie tes doigts blancs. Un trait de craie sèche sous les &lt;emphasis level="moderate"&gt;guidon&lt;/emphasis&gt;s. Un trait de craie sèche sur le ciment, net.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le long du blanc, l'avion glisse jusqu'à la porte. Tu as tenu, j'ai tracé. Le pneu n'a plus mangé la piste. Tes mains ont laissé la piste. On rentre, essuie tes doigts blancs. Un trait de craie sèche sur le ciment. Un trait de craie sèche sur le ciment, net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le long du blanc, l'avion glisse jusqu'à la porte. Tu as tenu, j'ai tracé. Le pneu n'a plus mangé la piste. Tes mains ont laissé la piste. On rentre, essuie tes doigts blancs. Un trait de craie sèche sous les &lt;emphasis&gt;guidon&lt;/emphasis&gt;s. Un trait de craie sèche sur le ciment, net.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -13539,7 +13539,7 @@
 enfant-m|Le pneu n'a plus mangé la piste.
 papa|Tes mains ont laissé la piste.
 maman|On rentre, essuie tes doigts blancs.
-narrateur|Un trait de craie sèche sur le ciment.
+narrateur|Un trait de craie sèche sous les guidons.
 narrateur|Un trait de craie sèche sur le ciment, net.</t>
         </is>
       </c>
@@ -15803,17 +15803,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Un trait blanc cherche la porte. Près du battant, le vent pousse la poussière. Mila allonge le trait, trop tôt. J'ouvre grand, pour voir dehors ! Le trait s'envole en poussière, trop loin. Ma piste a volé ! Le blanc disparaît vers le seuil. Ici, le vent prend le trait. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?</t>
+          <t>Un trait blanc cherche la porte. Près du battant, le vent pousse la poussière. Mila allonge le trait, trop tôt. J'ouvre grand, pour voir dehors ! Le trait s'envole en poussière, trop loin. Ma piste a volé ! Le blanc disparaît vers le seuil. Ici, le vent prend le trait. Sans le vent, le trait resterait. Alors on fait comment ? Tu vois comment, avec lui ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Un trait blanc cherche la porte. Près du battant, le &lt;emphasis level="moderate"&gt;vent&lt;/emphasis&gt; pousse la poussière. Mila allonge le trait, trop tôt. J'ouvre grand, pour voir dehors ! Le trait s'envole en poussière, trop loin. Ma piste a volé ! Le blanc disparaît vers le seuil. Ici, le vent prend le trait. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="-2st"&gt;Un trait blanc cherche la porte. Près du battant, le &lt;emphasis level="moderate"&gt;vent&lt;/emphasis&gt; pousse la poussière. Mila allonge le trait, trop tôt. J'ouvre grand, pour voir dehors ! Le trait s'envole en poussière, trop loin. Ma piste a volé ! Le blanc disparaît vers le seuil. Ici, le vent prend le trait. Sans le vent, le trait resterait. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/prosody&gt;&lt;break time="520ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;Un trait blanc cherche la porte. Près du battant, le &lt;emphasis&gt;vent&lt;/emphasis&gt; pousse la poussière. Mila allonge le trait, trop tôt. J'ouvre grand, pour voir dehors ! Le trait s'envole en poussière, trop loin. Ma piste a volé ! Le blanc disparaît vers le seuil. Ici, le vent prend le trait. Il lui faut un air plus calme. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/low-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;Un trait blanc cherche la porte. Près du battant, le &lt;emphasis&gt;vent&lt;/emphasis&gt; pousse la poussière. Mila allonge le trait, trop tôt. J'ouvre grand, pour voir dehors ! Le trait s'envole en poussière, trop loin. Ma piste a volé ! Le blanc disparaît vers le seuil. Ici, le vent prend le trait. Sans le vent, le trait resterait. Alors on fait comment ? Tu vois comment, avec lui ?&lt;/low-pitch&gt; [pause]</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -15959,7 +15959,7 @@
 enfant-f|Ma piste a volé !
 narrateur|Le blanc disparaît vers le seuil.
 papa|Ici, le vent prend le trait.
-maman|Il lui faut un air plus calme.
+maman|Sans le vent, le trait resterait.
 enfant-f|Alors on fait comment ?
 papa|Tu vois comment, avec lui ?</t>
         </is>
@@ -17290,7 +17290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17354,6 +17354,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
